--- a/data/trans_orig/P1420-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2012</t>
+          <t>Población con diagnóstico de hemorroides en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43479</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>29827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>955439</t>
+          <t>954688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>968913</t>
+          <t>969102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1294318</t>
+          <t>1296151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1317307</t>
+          <t>1317714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2257217</t>
+          <t>2257150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2282096</t>
+          <t>2282613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>33056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1942249</t>
+          <t>1943318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956727</t>
+          <t>1957584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1722079</t>
+          <t>1721536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1741599</t>
+          <t>1741112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3670139</t>
+          <t>3669641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3694489</t>
+          <t>3695488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472230</t>
+          <t>472762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480308</t>
+          <t>480316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447267</t>
+          <t>446795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456699</t>
+          <t>456697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924383</t>
+          <t>924500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935886</t>
+          <t>935996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>37470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>71214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,47 +1810,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>82788</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>66596</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>102416</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>82788</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>63246</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>100695</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3381633</t>
+          <t>3382312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3401795</t>
+          <t>3401831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3477595</t>
+          <t>3479806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3508827</t>
+          <t>3509656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,47 +1923,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6888013</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6868385</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6904205</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,81%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6888013</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6870106</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6907555</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2016</t>
+          <t>Población con diagnóstico de hemorroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>28680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42028</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735992</t>
+          <t>735504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748192</t>
+          <t>748740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>966013</t>
+          <t>965980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>984220</t>
+          <t>983156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1706979</t>
+          <t>1705281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1729278</t>
+          <t>1728624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,47 +2692,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23392</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>34954</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34686</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2051795</t>
+          <t>2050896</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2067411</t>
+          <t>2068020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,47 +2805,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1964908</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1953346</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1973931</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>98,82%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1964908</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1953614</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1973751</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4012960</t>
+          <t>4010498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4038392</t>
+          <t>4037478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10827</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528903</t>
+          <t>528742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544785</t>
+          <t>544036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538313</t>
+          <t>538483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548107</t>
+          <t>548100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073786</t>
+          <t>1070445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090523</t>
+          <t>1090543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>48583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>32788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62375</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62096</t>
+          <t>62707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99341</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3329883</t>
+          <t>3329035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3354430</t>
+          <t>3354376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3469725</t>
+          <t>3471277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499547</t>
+          <t>3499312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6810377</t>
+          <t>6808042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6847622</t>
+          <t>6847011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1420-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55290</t>
+          <t>56267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>954688</t>
+          <t>955179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>969102</t>
+          <t>969342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1296151</t>
+          <t>1296507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1317714</t>
+          <t>1317893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2257150</t>
+          <t>2256173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2282613</t>
+          <t>2282402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1943318</t>
+          <t>1942955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1957584</t>
+          <t>1957586</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1721536</t>
+          <t>1722167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1741112</t>
+          <t>1741680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3669641</t>
+          <t>3670278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3695488</t>
+          <t>3694917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472762</t>
+          <t>471889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480316</t>
+          <t>480299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446795</t>
+          <t>447952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456697</t>
+          <t>456687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924500</t>
+          <t>923958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935996</t>
+          <t>935922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37470</t>
+          <t>41638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41364</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71214</t>
+          <t>72145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66596</t>
+          <t>64489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102416</t>
+          <t>101086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3382312</t>
+          <t>3378144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3401831</t>
+          <t>3401646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3479806</t>
+          <t>3478875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3509656</t>
+          <t>3508739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6868385</t>
+          <t>6869715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6904205</t>
+          <t>6906312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18843</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>29122</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>41466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735504</t>
+          <t>736045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748740</t>
+          <t>748842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>965980</t>
+          <t>965538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>983156</t>
+          <t>983384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1705281</t>
+          <t>1707541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1728624</t>
+          <t>1729238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>53041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2050896</t>
+          <t>2050962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2068020</t>
+          <t>2068076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1953346</t>
+          <t>1953100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1973931</t>
+          <t>1973293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4010498</t>
+          <t>4011644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4037478</t>
+          <t>4036601</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528742</t>
+          <t>529730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544036</t>
+          <t>544261</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538483</t>
+          <t>536270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548100</t>
+          <t>548105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070445</t>
+          <t>1072460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090543</t>
+          <t>1090428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48583</t>
+          <t>48635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62707</t>
+          <t>62075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101676</t>
+          <t>100614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3329035</t>
+          <t>3328983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3354376</t>
+          <t>3354143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3471277</t>
+          <t>3471009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499312</t>
+          <t>3499852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6808042</t>
+          <t>6809104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6847011</t>
+          <t>6847643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
